--- a/artfynd/A 21041-2023 artfynd.xlsx
+++ b/artfynd/A 21041-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21041-2023 artfynd.xlsx
+++ b/artfynd/A 21041-2023 artfynd.xlsx
@@ -4710,10 +4710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117899933</v>
+        <v>117900958</v>
       </c>
       <c r="B41" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462519</v>
+        <v>462581</v>
       </c>
       <c r="R41" t="n">
-        <v>6735036</v>
+        <v>6735040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117900958</v>
+        <v>117899933</v>
       </c>
       <c r="B42" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462581</v>
+        <v>462519</v>
       </c>
       <c r="R42" t="n">
-        <v>6735040</v>
+        <v>6735036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 21041-2023 artfynd.xlsx
+++ b/artfynd/A 21041-2023 artfynd.xlsx
@@ -4506,10 +4506,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117899688</v>
+        <v>117900529</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462506</v>
+        <v>462563</v>
       </c>
       <c r="R39" t="n">
-        <v>6735016</v>
+        <v>6735096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117900267</v>
+        <v>117900958</v>
       </c>
       <c r="B40" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462555</v>
+        <v>462581</v>
       </c>
       <c r="R40" t="n">
-        <v>6735058</v>
+        <v>6735040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117900958</v>
+        <v>117900499</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462581</v>
+        <v>462547</v>
       </c>
       <c r="R41" t="n">
-        <v>6735040</v>
+        <v>6735090</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117899933</v>
+        <v>117900751</v>
       </c>
       <c r="B42" t="n">
-        <v>79098</v>
+        <v>8416</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4824,38 +4824,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroktjärnbäcken (Kroktjärnbäcken), Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462519</v>
+        <v>462620</v>
       </c>
       <c r="R42" t="n">
-        <v>6735036</v>
+        <v>6735048</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5016,7 +5021,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117899966</v>
+        <v>117900624</v>
       </c>
       <c r="B44" t="n">
         <v>78480</v>
@@ -5056,10 +5061,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462528</v>
+        <v>462598</v>
       </c>
       <c r="R44" t="n">
-        <v>6735018</v>
+        <v>6735084</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5118,7 +5123,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117900640</v>
+        <v>117900267</v>
       </c>
       <c r="B45" t="n">
         <v>78217</v>
@@ -5158,10 +5163,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462621</v>
+        <v>462555</v>
       </c>
       <c r="R45" t="n">
-        <v>6735109</v>
+        <v>6735058</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5322,7 +5327,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117900499</v>
+        <v>117899933</v>
       </c>
       <c r="B47" t="n">
         <v>79098</v>
@@ -5362,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462547</v>
+        <v>462519</v>
       </c>
       <c r="R47" t="n">
-        <v>6735090</v>
+        <v>6735036</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5424,10 +5429,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117900529</v>
+        <v>117899688</v>
       </c>
       <c r="B48" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5440,21 +5445,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5464,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462563</v>
+        <v>462506</v>
       </c>
       <c r="R48" t="n">
-        <v>6735096</v>
+        <v>6735016</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5526,7 +5531,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117900624</v>
+        <v>117900225</v>
       </c>
       <c r="B49" t="n">
         <v>78480</v>
@@ -5566,10 +5571,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462598</v>
+        <v>462530</v>
       </c>
       <c r="R49" t="n">
-        <v>6735084</v>
+        <v>6735041</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5628,10 +5633,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117900338</v>
+        <v>117900640</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5644,21 +5649,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462565</v>
+        <v>462621</v>
       </c>
       <c r="R50" t="n">
-        <v>6735077</v>
+        <v>6735109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5730,10 +5735,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117900751</v>
+        <v>117899966</v>
       </c>
       <c r="B51" t="n">
-        <v>8416</v>
+        <v>78480</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5742,43 +5747,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kroktjärnbäcken (Kroktjärnbäcken), Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462620</v>
+        <v>462528</v>
       </c>
       <c r="R51" t="n">
-        <v>6735048</v>
+        <v>6735018</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117900537</v>
+        <v>117900338</v>
       </c>
       <c r="B52" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462525</v>
+        <v>462565</v>
       </c>
       <c r="R52" t="n">
-        <v>6735068</v>
+        <v>6735077</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117900225</v>
+        <v>117900537</v>
       </c>
       <c r="B53" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462530</v>
+        <v>462525</v>
       </c>
       <c r="R53" t="n">
-        <v>6735041</v>
+        <v>6735068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 21041-2023 artfynd.xlsx
+++ b/artfynd/A 21041-2023 artfynd.xlsx
@@ -4506,10 +4506,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117900529</v>
+        <v>117899688</v>
       </c>
       <c r="B39" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462563</v>
+        <v>462506</v>
       </c>
       <c r="R39" t="n">
-        <v>6735096</v>
+        <v>6735016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117900958</v>
+        <v>117899933</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462581</v>
+        <v>462519</v>
       </c>
       <c r="R40" t="n">
-        <v>6735040</v>
+        <v>6735036</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117900499</v>
+        <v>117899966</v>
       </c>
       <c r="B41" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462547</v>
+        <v>462528</v>
       </c>
       <c r="R41" t="n">
-        <v>6735090</v>
+        <v>6735018</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117900751</v>
+        <v>117900225</v>
       </c>
       <c r="B42" t="n">
-        <v>8416</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4824,43 +4824,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kroktjärnbäcken (Kroktjärnbäcken), Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462620</v>
+        <v>462530</v>
       </c>
       <c r="R42" t="n">
-        <v>6735048</v>
+        <v>6735041</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4919,10 +4914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117900489</v>
+        <v>117900267</v>
       </c>
       <c r="B43" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462547</v>
+        <v>462555</v>
       </c>
       <c r="R43" t="n">
-        <v>6735090</v>
+        <v>6735058</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5021,10 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117900624</v>
+        <v>117900529</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5037,21 +5032,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5061,10 +5056,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462598</v>
+        <v>462563</v>
       </c>
       <c r="R44" t="n">
-        <v>6735084</v>
+        <v>6735096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5123,10 +5118,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117900267</v>
+        <v>117900751</v>
       </c>
       <c r="B45" t="n">
-        <v>78217</v>
+        <v>8416</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5135,38 +5130,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kroktjärnbäcken (Kroktjärnbäcken), Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462555</v>
+        <v>462620</v>
       </c>
       <c r="R45" t="n">
-        <v>6735058</v>
+        <v>6735048</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
         <v>117901265</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117899933</v>
+        <v>117900958</v>
       </c>
       <c r="B47" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462519</v>
+        <v>462581</v>
       </c>
       <c r="R47" t="n">
-        <v>6735036</v>
+        <v>6735040</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117899688</v>
+        <v>117900624</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462506</v>
+        <v>462598</v>
       </c>
       <c r="R48" t="n">
-        <v>6735016</v>
+        <v>6735084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5531,10 +5531,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117900225</v>
+        <v>117900537</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462530</v>
+        <v>462525</v>
       </c>
       <c r="R49" t="n">
-        <v>6735041</v>
+        <v>6735068</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117900640</v>
+        <v>117900338</v>
       </c>
       <c r="B50" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5649,21 +5649,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462621</v>
+        <v>462565</v>
       </c>
       <c r="R50" t="n">
-        <v>6735109</v>
+        <v>6735077</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117899966</v>
+        <v>117900499</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462528</v>
+        <v>462547</v>
       </c>
       <c r="R51" t="n">
-        <v>6735018</v>
+        <v>6735090</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117900338</v>
+        <v>117900640</v>
       </c>
       <c r="B52" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462565</v>
+        <v>462621</v>
       </c>
       <c r="R52" t="n">
-        <v>6735077</v>
+        <v>6735109</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117900537</v>
+        <v>117900489</v>
       </c>
       <c r="B53" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462525</v>
+        <v>462547</v>
       </c>
       <c r="R53" t="n">
-        <v>6735068</v>
+        <v>6735090</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
